--- a/artfynd/A 14221-2025 artfynd.xlsx
+++ b/artfynd/A 14221-2025 artfynd.xlsx
@@ -813,12 +813,7 @@
         <v>74982786</v>
       </c>
       <c r="B3" t="n">
-        <v>102632</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>105003</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -850,10 +845,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>453728.0621523782</v>
+        <v>453728</v>
       </c>
       <c r="R3" t="n">
-        <v>6382791.223721518</v>
+        <v>6382791</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -883,19 +878,9 @@
           <t>1997-07-14</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1997-07-14</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">

--- a/artfynd/A 14221-2025 artfynd.xlsx
+++ b/artfynd/A 14221-2025 artfynd.xlsx
@@ -813,7 +813,7 @@
         <v>74982786</v>
       </c>
       <c r="B3" t="n">
-        <v>105003</v>
+        <v>105012</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 14221-2025 artfynd.xlsx
+++ b/artfynd/A 14221-2025 artfynd.xlsx
@@ -813,7 +813,7 @@
         <v>74982786</v>
       </c>
       <c r="B3" t="n">
-        <v>105012</v>
+        <v>105015</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 14221-2025 artfynd.xlsx
+++ b/artfynd/A 14221-2025 artfynd.xlsx
@@ -813,7 +813,7 @@
         <v>74982786</v>
       </c>
       <c r="B3" t="n">
-        <v>105015</v>
+        <v>105043</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 14221-2025 artfynd.xlsx
+++ b/artfynd/A 14221-2025 artfynd.xlsx
@@ -813,7 +813,7 @@
         <v>74982786</v>
       </c>
       <c r="B3" t="n">
-        <v>105043</v>
+        <v>105049</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 14221-2025 artfynd.xlsx
+++ b/artfynd/A 14221-2025 artfynd.xlsx
@@ -813,7 +813,7 @@
         <v>74982786</v>
       </c>
       <c r="B3" t="n">
-        <v>105049</v>
+        <v>105056</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 14221-2025 artfynd.xlsx
+++ b/artfynd/A 14221-2025 artfynd.xlsx
@@ -813,7 +813,7 @@
         <v>74982786</v>
       </c>
       <c r="B3" t="n">
-        <v>105056</v>
+        <v>105060</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 14221-2025 artfynd.xlsx
+++ b/artfynd/A 14221-2025 artfynd.xlsx
@@ -813,7 +813,7 @@
         <v>74982786</v>
       </c>
       <c r="B3" t="n">
-        <v>105060</v>
+        <v>105067</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 14221-2025 artfynd.xlsx
+++ b/artfynd/A 14221-2025 artfynd.xlsx
@@ -813,7 +813,7 @@
         <v>74982786</v>
       </c>
       <c r="B3" t="n">
-        <v>105070</v>
+        <v>105075</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 14221-2025 artfynd.xlsx
+++ b/artfynd/A 14221-2025 artfynd.xlsx
@@ -813,7 +813,7 @@
         <v>74982786</v>
       </c>
       <c r="B3" t="n">
-        <v>105075</v>
+        <v>105083</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 14221-2025 artfynd.xlsx
+++ b/artfynd/A 14221-2025 artfynd.xlsx
@@ -813,7 +813,7 @@
         <v>74982786</v>
       </c>
       <c r="B3" t="n">
-        <v>105083</v>
+        <v>105093</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 14221-2025 artfynd.xlsx
+++ b/artfynd/A 14221-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>467699</v>
       </c>
       <c r="B2" t="n">
-        <v>102631</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>105598</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>453766.9832520686</v>
+        <v>453767</v>
       </c>
       <c r="R2" t="n">
-        <v>6382812.761119792</v>
+        <v>6382813</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +749,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>F-Jön-0238</t>
+          <t>Arkiv-F-Jön-0357</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -762,19 +757,9 @@
           <t>1997-07-14</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1997-07-14</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -804,16 +789,16 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>Floraväkteri Sverige</t>
+          <t>Arkiv Floraväktarlokaler</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>74982786</v>
+        <v>74982782</v>
       </c>
       <c r="B3" t="n">
-        <v>105093</v>
+        <v>105597</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -875,17 +860,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>1997-07-14</t>
+          <t>2000-06-11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1997-07-14</t>
+          <t>2000-06-11</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 6E7b 0505. SOM: Silene dichotoma. LEG: Ragnar Lernedal. KOM: 4 plantor</t>
+          <t>Smålands flora 2007: KOO: 6E7b 0505. SOM: Silene dichotoma. LEG: Ragnar Lernedal. KOM: 0 plantor</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 14221-2025 artfynd.xlsx
+++ b/artfynd/A 14221-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -792,6 +797,11 @@
           <t>Arkiv Floraväktarlokaler</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/467699</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -903,8 +913,17 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74982782</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>